--- a/Decks/Kresh.xlsx
+++ b/Decks/Kresh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1063BBEB-C769-4D7A-A42A-92ACAE611A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D93D12-9866-49C9-9EE5-0E7B858C2D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{39A5921C-0970-4177-82E8-8E245F74B9B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39A5921C-0970-4177-82E8-8E245F74B9B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Kresh" sheetId="1" r:id="rId1"/>
@@ -305,9 +305,6 @@
     <t>Life's Legacy</t>
   </si>
   <si>
-    <t>Mask of Griselbrand</t>
-  </si>
-  <si>
     <t>Morbid Opportunist</t>
   </si>
   <si>
@@ -369,6 +366,9 @@
   </si>
   <si>
     <t>Shared Roots</t>
+  </si>
+  <si>
+    <t>Surrak, Elusive Hunter</t>
   </si>
 </sst>
 </file>
@@ -1398,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>68</v>
@@ -1923,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2043,10 +2043,10 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2103,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2133,160 +2133,160 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="D92" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="D97" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Kresh.xlsx
+++ b/Decks/Kresh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D93D12-9866-49C9-9EE5-0E7B858C2D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128F9A15-2DA4-4C18-B096-4C659E2FF318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39A5921C-0970-4177-82E8-8E245F74B9B3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="106">
   <si>
     <t>Função</t>
   </si>
@@ -191,12 +191,6 @@
     <t>Terminate</t>
   </si>
   <si>
-    <t>Outland Liberator</t>
-  </si>
-  <si>
-    <t>Artifact Mutation</t>
-  </si>
-  <si>
     <t>Krosan Grip</t>
   </si>
   <si>
@@ -257,9 +251,6 @@
     <t>Hidetsugu Consumes All</t>
   </si>
   <si>
-    <t>Bane of Progress</t>
-  </si>
-  <si>
     <t>Ritual of Soot</t>
   </si>
   <si>
@@ -269,9 +260,6 @@
     <t>Nibelheim Aflame</t>
   </si>
   <si>
-    <t>Pestilence</t>
-  </si>
-  <si>
     <t>Soul Immolation</t>
   </si>
   <si>
@@ -284,9 +272,6 @@
     <t>Draw</t>
   </si>
   <si>
-    <t>Jarad, Golgari Lich Lord</t>
-  </si>
-  <si>
     <t>Phyrexian Arena</t>
   </si>
   <si>
@@ -317,12 +302,6 @@
     <t>Beifong's Bounty Hunters</t>
   </si>
   <si>
-    <t>Feldon of the Third Path</t>
-  </si>
-  <si>
-    <t>Red XIII, Proud Warrior</t>
-  </si>
-  <si>
     <t>Loxodon Warhammer</t>
   </si>
   <si>
@@ -335,9 +314,6 @@
     <t>Soul's Fire</t>
   </si>
   <si>
-    <t>Thud</t>
-  </si>
-  <si>
     <t>Rite of Consumption</t>
   </si>
   <si>
@@ -353,9 +329,6 @@
     <t>Electric Seaweed</t>
   </si>
   <si>
-    <t>Clackbridge Troll</t>
-  </si>
-  <si>
     <t>Terrasymbiosis</t>
   </si>
   <si>
@@ -369,6 +342,18 @@
   </si>
   <si>
     <t>Surrak, Elusive Hunter</t>
+  </si>
+  <si>
+    <t>Fight for the Throne</t>
+  </si>
+  <si>
+    <t>Solemn Simulacrum</t>
+  </si>
+  <si>
+    <t>Larval Scoutlander</t>
+  </si>
+  <si>
+    <t>Nova Flame</t>
   </si>
 </sst>
 </file>
@@ -809,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B68" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1398,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1469,14 +1454,14 @@
         <v>27</v>
       </c>
       <c r="B47" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C47&lt;&gt;D47</f>
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,13 +1470,13 @@
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,43 +1485,43 @@
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B50" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C50&lt;&gt;D50</f>
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1548,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1563,40 +1548,40 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1623,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1635,13 +1620,13 @@
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1653,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1668,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1680,13 +1665,13 @@
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1698,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1710,583 +1695,583 @@
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>57</v>
+      </c>
+      <c r="B67" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="D67" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B69:B101" si="1">C69&lt;&gt;D69</f>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>68</v>
+      </c>
+      <c r="B77" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B77" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="D77" s="4" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C79&lt;&gt;D79</f>
+        <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>77</v>
+      </c>
+      <c r="B88" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B88" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="D88" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
